--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486440_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486440_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0192</v>
+        <v>3.5394</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9832</v>
+        <v>4.3185</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9639</v>
+        <v>-0.779</v>
       </c>
       <c r="G2" t="n">
         <v>3.2733</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6408</v>
+        <v>-1.1206</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0243</v>
+        <v>-0.8394</v>
       </c>
       <c r="V2" t="n">
         <v>1.3867</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1544</v>
+        <v>3.2179</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0579</v>
+        <v>6.505</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.9036</v>
+        <v>-3.2871</v>
       </c>
       <c r="G3" t="n">
         <v>4.8788</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1765</v>
+        <v>-0.113</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6934</v>
+        <v>-0.2463</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4831</v>
+        <v>0.1334</v>
       </c>
       <c r="V3" t="n">
         <v>-0.678</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5911</v>
+        <v>0.9996</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4777</v>
+        <v>0.7012</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1134</v>
+        <v>0.2984</v>
       </c>
       <c r="G4" t="n">
         <v>-1.2663</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6853</v>
+        <v>-1.2768</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0688</v>
+        <v>-0.8839</v>
       </c>
       <c r="V4" t="n">
         <v>2.4552</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SEOANE RODICIO</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1336</v>
+        <v>-0.1479</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3414</v>
+        <v>0.497</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2078</v>
+        <v>-0.6449</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7465</v>
+        <v>1.9073</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2249</v>
+        <v>1.2132</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9714</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1254</v>
+        <v>1.8485</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8276</v>
+        <v>0.9855</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.953</v>
+        <v>0.863</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6211</v>
+        <v>0.0588</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6027</v>
+        <v>0.2277</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0184</v>
+        <v>-0.1689</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.613</v>
+        <v>-0.6594</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6934</v>
+        <v>-0.3064</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3063</v>
+        <v>-0.353</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3082</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4382</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>R. SEOANE RODICIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6874</v>
+        <v>-0.2722</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0499</v>
+        <v>-0.8943</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7373</v>
+        <v>0.6222</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9073</v>
+        <v>-1.7465</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2132</v>
+        <v>0.2249</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6941000000000001</v>
+        <v>-1.9714</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8485</v>
+        <v>-0.1254</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9855</v>
+        <v>0.8276</v>
       </c>
       <c r="L7" t="n">
-        <v>0.863</v>
+        <v>-0.953</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0588</v>
+        <v>-1.6211</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2277</v>
+        <v>-0.6027</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1689</v>
+        <v>-1.0184</v>
       </c>
       <c r="P7" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1989</v>
+        <v>0.4744</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.2463</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4455</v>
+        <v>0.7207</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3082</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4382</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1611</v>
+        <v>-1.3653</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1443</v>
+        <v>2.0326</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3054</v>
+        <v>-3.3979</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4285</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5772</v>
+        <v>-0.7814</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1202</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5688</v>
+        <v>-0.6612</v>
       </c>
       <c r="V8" t="n">
         <v>-1.243</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0646</v>
+        <v>-1.5945</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4833</v>
+        <v>-0.2598</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5813</v>
+        <v>-1.3347</v>
       </c>
       <c r="G9" t="n">
         <v>-0.251</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9436</v>
+        <v>-0.4735</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5564</v>
+        <v>-0.3329</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3872</v>
+        <v>-0.1406</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9571</v>
+        <v>-4.0519</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5432</v>
+        <v>-6.1663</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5004</v>
+        <v>2.1143</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7536</v>
+        <v>-5.4389</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5384</v>
+        <v>-1.4722</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2152</v>
+        <v>-3.9667</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5175999999999999</v>
+        <v>-5.0841</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2857</v>
+        <v>-1.4354</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8032</v>
+        <v>-3.6488</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2712</v>
+        <v>-0.3548</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2528</v>
+        <v>-0.0368</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0184</v>
+        <v>-0.318</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3445</v>
+        <v>0.6474</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0707</v>
+        <v>-0.1899</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2737</v>
+        <v>0.8373</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.808</v>
+        <v>0.7395</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9379</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1426</v>
+        <v>-4.4446</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7193</v>
+        <v>-0.5744</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5767</v>
+        <v>-3.8702</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.4389</v>
+        <v>-0.7536</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4722</v>
+        <v>-0.5384</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.9667</v>
+        <v>-0.2152</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.0841</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4354</v>
+        <v>-0.2857</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.6488</v>
+        <v>0.8032</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3548</v>
+        <v>-1.2712</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0368</v>
+        <v>-0.2528</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.318</v>
+        <v>-1.0184</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5568</v>
+        <v>-0.143</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2572</v>
+        <v>-0.0469</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2996</v>
+        <v>-0.0961</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7395</v>
+        <v>-1.808</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5443</v>
+        <v>-2.9379</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1895</v>
+        <v>-4.4516</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8339</v>
+        <v>-3.281</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3556</v>
+        <v>-1.1706</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4702</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1714</v>
+        <v>-0.0907</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5997</v>
+        <v>0.1526</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4283</v>
+        <v>-0.2434</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5857</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.5442</v>
+        <v>-8.5441</v>
       </c>
       <c r="E13" t="n">
-        <v>4.017800000000002</v>
+        <v>4.018000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.5621</v>
+        <v>-12.562</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.200099999999999</v>
+        <v>-2.2001</v>
       </c>
       <c r="H13" t="n">
         <v>-8.136700000000001</v>
@@ -1444,7 +1444,7 @@
         <v>10.002</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.784</v>
+        <v>-3.784000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>13.7857</v>
@@ -1468,13 +1468,13 @@
         <v>11.9626</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6051</v>
+        <v>-3.605099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.079</v>
+        <v>-2.0789</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5264</v>
+        <v>-1.5262</v>
       </c>
       <c r="V13" t="n">
         <v>0.5234999999999997</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5939</v>
+        <v>4.8</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1495</v>
+        <v>3.479</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4443</v>
+        <v>1.321</v>
       </c>
       <c r="G14" t="n">
         <v>1.0507</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5209</v>
+        <v>0.727</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9782</v>
+        <v>0.3076</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5427</v>
+        <v>0.4194</v>
       </c>
       <c r="V14" t="n">
         <v>1.4997</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3855</v>
+        <v>4.5468</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1988</v>
+        <v>6.9166</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8133</v>
+        <v>-2.3698</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0583</v>
+        <v>2.1552</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9995</v>
+        <v>-1.3135</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9411</v>
+        <v>3.4687</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0705</v>
+        <v>4.64</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1238</v>
+        <v>-1.0791</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0533</v>
+        <v>5.7191</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0121</v>
+        <v>-2.4847</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8757</v>
+        <v>-0.2344</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8878</v>
+        <v>-2.2504</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5215</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7607</v>
+        <v>0.5816</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1937</v>
+        <v>-0.0601</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3252</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4552</v>
+        <v>1.695</v>
       </c>
       <c r="X15" t="n">
         <v>-1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3504</v>
+        <v>3.9615</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1371</v>
+        <v>4.5282</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7867</v>
+        <v>-0.5667</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4395</v>
+        <v>2.0583</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2553</v>
+        <v>3.9995</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6948</v>
+        <v>-1.9411</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6461</v>
+        <v>3.0705</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.319</v>
+        <v>3.1238</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9651</v>
+        <v>-0.0533</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2066</v>
+        <v>-1.0121</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0636</v>
+        <v>0.8757</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2703</v>
+        <v>-1.8878</v>
       </c>
       <c r="P16" t="n">
         <v>0.435</v>
@@ -1702,28 +1702,28 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3905</v>
+        <v>0.143</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2019</v>
+        <v>0.0901</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5923</v>
+        <v>0.0529</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0854</v>
+        <v>1.3252</v>
       </c>
       <c r="W16" t="n">
-        <v>3.7804</v>
+        <v>2.4552</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3233</v>
+        <v>3.233</v>
       </c>
       <c r="E17" t="n">
-        <v>6.693</v>
+        <v>4.9136</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3698</v>
+        <v>-1.6806</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1552</v>
+        <v>0.4395</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3135</v>
+        <v>-0.2553</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4687</v>
+        <v>0.6948</v>
       </c>
       <c r="J17" t="n">
-        <v>4.64</v>
+        <v>2.6461</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0791</v>
+        <v>-0.319</v>
       </c>
       <c r="L17" t="n">
-        <v>5.7191</v>
+        <v>2.9651</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4847</v>
+        <v>-2.2066</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2344</v>
+        <v>0.0636</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2504</v>
+        <v>-2.2703</v>
       </c>
       <c r="P17" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.298</v>
+        <v>0.2731</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3581</v>
+        <v>-0.4254</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0601</v>
+        <v>0.6985</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.0854</v>
       </c>
       <c r="W17" t="n">
-        <v>1.695</v>
+        <v>3.7804</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6691</v>
+        <v>1.4879</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8786</v>
+        <v>3.5433</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2095</v>
+        <v>-2.0554</v>
       </c>
       <c r="G18" t="n">
         <v>0.1974</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1014</v>
+        <v>0.9202</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9542</v>
+        <v>0.6189</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1472</v>
+        <v>0.3013</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9347</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3627</v>
+        <v>0.5669</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0365</v>
+        <v>0.1483</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3262</v>
+        <v>0.4187</v>
       </c>
       <c r="G19" t="n">
         <v>0.5991</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2364</v>
+        <v>-0.0321</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3005</v>
+        <v>0.2788</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7208</v>
+        <v>-1.9224</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0212</v>
+        <v>2.2012</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2132</v>
+        <v>1.6747</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9399</v>
+        <v>2.1775</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7267</v>
+        <v>-0.5028</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.825</v>
+        <v>1.3059</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1182</v>
+        <v>1.1529</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7068</v>
+        <v>0.153</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0382</v>
+        <v>0.3688</v>
       </c>
       <c r="N20" t="n">
-        <v>1.0582</v>
+        <v>1.0247</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0199</v>
+        <v>-0.6558</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6321</v>
+        <v>-0.0261</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1717</v>
+        <v>-0.3136</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4605</v>
+        <v>0.2875</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1952</v>
+        <v>-0.9347</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2981</v>
+        <v>-0.2814</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8106</v>
+        <v>-3.056</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1087</v>
+        <v>2.7747</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6747</v>
+        <v>0.2132</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1775</v>
+        <v>0.9399</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5028</v>
+        <v>-0.7267</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3059</v>
+        <v>-0.825</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1529</v>
+        <v>-0.1182</v>
       </c>
       <c r="L21" t="n">
-        <v>0.153</v>
+        <v>-0.7068</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3688</v>
+        <v>1.0382</v>
       </c>
       <c r="N21" t="n">
-        <v>1.0247</v>
+        <v>1.0582</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6558</v>
+        <v>-0.0199</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0068</v>
+        <v>1.0503</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2019</v>
+        <v>0.8364</v>
       </c>
       <c r="U21" t="n">
-        <v>0.195</v>
+        <v>0.2139</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9347</v>
+        <v>0.1952</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1918</v>
+        <v>-1.2245</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6906</v>
+        <v>1.4729</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8824</v>
+        <v>-2.6974</v>
       </c>
       <c r="G22" t="n">
         <v>-0.223</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8393</v>
+        <v>0.128</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.0288</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0858</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4345</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4148</v>
+        <v>-3.8214</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3094</v>
+        <v>-4.0859</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1053</v>
+        <v>0.2645</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2346</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1149</v>
+        <v>-0.5215</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8099</v>
+        <v>-0.5864</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.305</v>
+        <v>0.0649</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1327</v>
+        <v>-5.0036</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3813</v>
+        <v>-3.3754</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7515</v>
+        <v>-1.6282</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7304</v>
@@ -2326,13 +2326,13 @@
         <v>2.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7073</v>
+        <v>0.4218</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7294</v>
+        <v>0.2764</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0221</v>
+        <v>0.1454</v>
       </c>
       <c r="V24" t="n">
         <v>-1.695</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.544200000000004</v>
+        <v>8.544</v>
       </c>
       <c r="E25" t="n">
-        <v>12.562</v>
+        <v>12.5622</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.018100000000001</v>
+        <v>-4.018000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>2.200099999999999</v>
@@ -2383,7 +2383,7 @@
         <v>4.3528</v>
       </c>
       <c r="L25" t="n">
-        <v>7.849000000000002</v>
+        <v>7.848999999999998</v>
       </c>
       <c r="M25" t="n">
         <v>-10.0017</v>
@@ -2407,10 +2407,10 @@
         <v>3.6052</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5263</v>
+        <v>1.5262</v>
       </c>
       <c r="U25" t="n">
-        <v>2.0788</v>
+        <v>2.0789</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5236000000000001</v>
